--- a/input/03_input_bapp_pml_t2.xlsx
+++ b/input/03_input_bapp_pml_t2.xlsx
@@ -51,7 +51,7 @@
     <t>251</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1DdS13-wYZPXULgFupJmOlEUnao8hM5r4</t>
+    <t>https://example.go.id/api/dokumen/123/gambar</t>
   </si>
   <si>
     <t>Nama Lengkap</t>
